--- a/proyFinal/src/datos/planilla_pagos.xlsx
+++ b/proyFinal/src/datos/planilla_pagos.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t xml:space="preserve"> DNI Deportista</t>
   </si>
@@ -21,9 +21,6 @@
   <si>
     <t>Fecha Vencimiento</t>
   </si>
-  <si>
-    <t>IdEstado</t>
-  </si>
 </sst>
 </file>
 
@@ -32,12 +29,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
     <font>
       <color theme="1"/>
@@ -64,9 +65,9 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -281,6 +282,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="3" max="3" width="18.13"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -292,9 +296,7 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="D1" s="1"/>
     </row>
     <row r="2">
       <c r="B2" s="2"/>
@@ -311,6 +313,374 @@
     <row r="5">
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+    </row>
+    <row r="42">
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+    </row>
+    <row r="43">
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+    </row>
+    <row r="45">
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+    </row>
+    <row r="47">
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+    </row>
+    <row r="48">
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+    </row>
+    <row r="51">
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+    </row>
+    <row r="52">
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+    </row>
+    <row r="53">
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+    </row>
+    <row r="54">
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+    </row>
+    <row r="55">
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+    </row>
+    <row r="56">
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+    </row>
+    <row r="57">
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+    </row>
+    <row r="58">
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+    </row>
+    <row r="59">
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+    </row>
+    <row r="60">
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+    </row>
+    <row r="61">
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+    </row>
+    <row r="62">
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+    </row>
+    <row r="63">
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+    </row>
+    <row r="64">
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+    </row>
+    <row r="65">
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+    </row>
+    <row r="66">
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+    </row>
+    <row r="67">
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+    </row>
+    <row r="68">
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+    </row>
+    <row r="69">
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+    </row>
+    <row r="70">
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+    </row>
+    <row r="71">
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+    </row>
+    <row r="72">
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+    </row>
+    <row r="73">
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+    </row>
+    <row r="74">
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+    </row>
+    <row r="75">
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+    </row>
+    <row r="76">
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+    </row>
+    <row r="77">
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+    </row>
+    <row r="78">
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+    </row>
+    <row r="79">
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+    </row>
+    <row r="80">
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+    </row>
+    <row r="81">
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+    </row>
+    <row r="82">
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+    </row>
+    <row r="83">
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+    </row>
+    <row r="84">
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+    </row>
+    <row r="85">
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+    </row>
+    <row r="86">
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+    </row>
+    <row r="87">
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
+    </row>
+    <row r="88">
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+    </row>
+    <row r="89">
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+    </row>
+    <row r="90">
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+    </row>
+    <row r="91">
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+    </row>
+    <row r="92">
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+    </row>
+    <row r="93">
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+    </row>
+    <row r="94">
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+    </row>
+    <row r="95">
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+    </row>
+    <row r="96">
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+    </row>
+    <row r="97">
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
